--- a/datasets/sztabowa/archive/ceny_2026-10-28.xlsx
+++ b/datasets/sztabowa/archive/ceny_2026-10-28.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7A1C851-F628-4B38-8A2D-99C8055C955E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{557A5A5B-4CD9-4D43-A6C7-D2AFCC741734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-708" windowWidth="23256" windowHeight="13896" xr2:uid="{336D2583-5C4C-4C42-9206-61D546232E49}"/>
   </bookViews>
@@ -966,20 +966,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA33353A-1A07-421F-B982-7CDBB172178E}">
   <dimension ref="A1:BF82"/>
-  <sheetFormatPr defaultColWidth="27.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="27.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="37" width="27.7109375" style="3"/>
-    <col min="38" max="38" width="27.7109375" style="8"/>
-    <col min="39" max="39" width="27.7109375" style="3"/>
-    <col min="40" max="40" width="27.7109375" style="8"/>
-    <col min="41" max="41" width="27.7109375" style="3"/>
-    <col min="42" max="42" width="27.7109375" style="8"/>
-    <col min="43" max="45" width="27.7109375" style="3"/>
-    <col min="46" max="46" width="27.7109375" style="8"/>
-    <col min="47" max="16384" width="27.7109375" style="3"/>
+    <col min="1" max="37" width="27.6640625" style="3"/>
+    <col min="38" max="38" width="27.6640625" style="8"/>
+    <col min="39" max="39" width="27.6640625" style="3"/>
+    <col min="40" max="40" width="27.6640625" style="8"/>
+    <col min="41" max="41" width="27.6640625" style="3"/>
+    <col min="42" max="42" width="27.6640625" style="8"/>
+    <col min="43" max="45" width="27.6640625" style="3"/>
+    <col min="46" max="46" width="27.6640625" style="8"/>
+    <col min="47" max="16384" width="27.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58" s="10" customFormat="1" ht="135" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:58" s="10" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1155,7 +1155,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:58" s="14" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:58" s="14" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>64</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="3" spans="1:58" s="14" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:58" s="14" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>64</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="4" spans="1:58" s="14" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:58" s="14" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>64</v>
       </c>
@@ -1683,7 +1683,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="5" spans="1:58" s="14" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:58" s="14" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>64</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:58" s="14" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:58" s="14" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>64</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="7" spans="1:58" s="14" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:58" s="14" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>64</v>
       </c>
@@ -2211,7 +2211,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="8" spans="1:58" s="14" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:58" s="14" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>64</v>
       </c>
@@ -2387,7 +2387,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="9" spans="1:58" s="14" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:58" s="14" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>64</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="10" spans="1:58" s="14" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:58" s="14" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>64</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="11" spans="1:58" s="14" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:58" s="14" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>64</v>
       </c>
@@ -2915,7 +2915,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="12" spans="1:58" s="14" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:58" s="14" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>64</v>
       </c>
@@ -3091,7 +3091,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="13" spans="1:58" s="14" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:58" s="14" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>64</v>
       </c>
@@ -3267,7 +3267,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="14" spans="1:58" s="14" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:58" s="14" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>64</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="15" spans="1:58" s="14" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:58" s="14" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>64</v>
       </c>
@@ -3619,7 +3619,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="16" spans="1:58" s="14" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:58" s="14" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>64</v>
       </c>
@@ -3795,7 +3795,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="17" spans="1:58" s="14" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:58" s="14" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>64</v>
       </c>
@@ -3971,7 +3971,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="18" spans="1:58" s="14" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:58" s="14" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>64</v>
       </c>
@@ -4147,7 +4147,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="19" spans="1:58" s="14" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:58" s="14" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>64</v>
       </c>
@@ -4323,7 +4323,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="20" spans="1:58" s="14" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:58" s="14" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>64</v>
       </c>
@@ -4499,7 +4499,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="21" spans="1:58" s="14" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:58" s="14" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>64</v>
       </c>
@@ -4675,7 +4675,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="22" spans="1:58" s="14" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:58" s="14" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>64</v>
       </c>
@@ -4851,7 +4851,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="23" spans="1:58" s="14" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:58" s="14" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>64</v>
       </c>
@@ -5027,7 +5027,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="24" spans="1:58" s="14" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:58" s="14" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>64</v>
       </c>
@@ -5203,7 +5203,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="25" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>64</v>
       </c>
@@ -5379,7 +5379,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="26" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>64</v>
       </c>
@@ -5555,7 +5555,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="27" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>64</v>
       </c>
@@ -5731,7 +5731,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="28" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>64</v>
       </c>
@@ -5907,7 +5907,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="29" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>64</v>
       </c>
@@ -6083,7 +6083,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="30" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>64</v>
       </c>
@@ -6259,7 +6259,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="31" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>64</v>
       </c>
@@ -6435,7 +6435,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="32" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>64</v>
       </c>
@@ -6611,7 +6611,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="33" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>64</v>
       </c>
@@ -6787,7 +6787,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="34" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>64</v>
       </c>
@@ -6963,7 +6963,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="35" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>64</v>
       </c>
@@ -7139,7 +7139,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="36" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>64</v>
       </c>
@@ -7315,7 +7315,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="37" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>64</v>
       </c>
@@ -7491,7 +7491,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="38" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>64</v>
       </c>
@@ -7667,7 +7667,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="39" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>64</v>
       </c>
@@ -7843,7 +7843,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="40" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>64</v>
       </c>
@@ -8019,7 +8019,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="41" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>64</v>
       </c>
@@ -8195,7 +8195,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="42" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>64</v>
       </c>
@@ -8371,7 +8371,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="43" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>64</v>
       </c>
@@ -8547,7 +8547,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="44" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>64</v>
       </c>
@@ -8723,7 +8723,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="45" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>64</v>
       </c>
@@ -8899,7 +8899,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="46" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>64</v>
       </c>
@@ -9075,7 +9075,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="47" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>64</v>
       </c>
@@ -9251,7 +9251,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="48" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>64</v>
       </c>
@@ -9427,7 +9427,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="49" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>64</v>
       </c>
@@ -9564,7 +9564,7 @@
         <v>105</v>
       </c>
       <c r="AT49" s="28">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AU49" s="6">
         <v>45825</v>
@@ -9603,7 +9603,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="50" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>64</v>
       </c>
@@ -9740,7 +9740,7 @@
         <v>106</v>
       </c>
       <c r="AT50" s="28">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AU50" s="6">
         <v>45825</v>
@@ -9779,7 +9779,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="51" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>64</v>
       </c>
@@ -9916,7 +9916,7 @@
         <v>107</v>
       </c>
       <c r="AT51" s="28">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AU51" s="6">
         <v>45825</v>
@@ -9955,7 +9955,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="52" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>64</v>
       </c>
@@ -10092,7 +10092,7 @@
         <v>108</v>
       </c>
       <c r="AT52" s="28">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AU52" s="6">
         <v>45825</v>
@@ -10131,7 +10131,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="53" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>64</v>
       </c>
@@ -10268,7 +10268,7 @@
         <v>109</v>
       </c>
       <c r="AT53" s="29">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AU53" s="6">
         <v>45825</v>
@@ -10307,7 +10307,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="54" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>64</v>
       </c>
@@ -10444,7 +10444,7 @@
         <v>110</v>
       </c>
       <c r="AT54" s="28">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AU54" s="6">
         <v>45825</v>
@@ -10483,7 +10483,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="55" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>64</v>
       </c>
@@ -10620,7 +10620,7 @@
         <v>111</v>
       </c>
       <c r="AT55" s="28">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AU55" s="6">
         <v>45825</v>
@@ -10659,7 +10659,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="56" spans="1:58" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:58" ht="78" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>64</v>
       </c>
@@ -10796,7 +10796,7 @@
         <v>112</v>
       </c>
       <c r="AT56" s="28">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AU56" s="6">
         <v>45825</v>
@@ -10835,7 +10835,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="57" spans="1:58" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:58" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="23"/>
       <c r="B57" s="23"/>
       <c r="I57" s="24"/>
@@ -10857,7 +10857,7 @@
       <c r="BD57" s="24"/>
       <c r="BE57" s="31"/>
     </row>
-    <row r="58" spans="1:58" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:58" ht="15.6" x14ac:dyDescent="0.3">
       <c r="I58" s="24"/>
       <c r="AL58" s="15"/>
       <c r="AM58" s="16"/>
@@ -10867,7 +10867,7 @@
       <c r="AW58" s="23"/>
       <c r="AX58" s="24"/>
     </row>
-    <row r="59" spans="1:58" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:58" ht="15.6" x14ac:dyDescent="0.3">
       <c r="AL59" s="15"/>
       <c r="AM59" s="16"/>
       <c r="AN59" s="15"/>
@@ -10876,7 +10876,7 @@
       <c r="AW59" s="23"/>
       <c r="AX59" s="24"/>
     </row>
-    <row r="60" spans="1:58" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:58" ht="15.6" x14ac:dyDescent="0.3">
       <c r="AL60" s="15"/>
       <c r="AM60" s="16"/>
       <c r="AN60" s="15"/>
@@ -10885,7 +10885,7 @@
       <c r="AW60" s="23"/>
       <c r="AX60" s="24"/>
     </row>
-    <row r="61" spans="1:58" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:58" ht="15.6" x14ac:dyDescent="0.3">
       <c r="AL61" s="15"/>
       <c r="AM61" s="16"/>
       <c r="AN61" s="15"/>
@@ -10893,7 +10893,7 @@
       <c r="AV61" s="23"/>
       <c r="AW61" s="23"/>
     </row>
-    <row r="62" spans="1:58" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:58" ht="15.6" x14ac:dyDescent="0.3">
       <c r="AL62" s="15"/>
       <c r="AM62" s="16"/>
       <c r="AN62" s="15"/>
@@ -10901,7 +10901,7 @@
       <c r="AV62" s="23"/>
       <c r="AW62" s="23"/>
     </row>
-    <row r="63" spans="1:58" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:58" ht="15.6" x14ac:dyDescent="0.3">
       <c r="AL63" s="15"/>
       <c r="AM63" s="16"/>
       <c r="AN63" s="15"/>
@@ -10909,7 +10909,7 @@
       <c r="AV63" s="23"/>
       <c r="AW63" s="23"/>
     </row>
-    <row r="64" spans="1:58" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:58" ht="15.6" x14ac:dyDescent="0.3">
       <c r="AL64" s="15"/>
       <c r="AM64" s="16"/>
       <c r="AN64" s="15"/>
@@ -10917,7 +10917,7 @@
       <c r="AV64" s="23"/>
       <c r="AW64" s="23"/>
     </row>
-    <row r="65" spans="38:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="38:49" ht="15.6" x14ac:dyDescent="0.3">
       <c r="AL65" s="15"/>
       <c r="AM65" s="16"/>
       <c r="AN65" s="15"/>
@@ -10925,7 +10925,7 @@
       <c r="AV65" s="23"/>
       <c r="AW65" s="23"/>
     </row>
-    <row r="66" spans="38:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="38:49" ht="15.6" x14ac:dyDescent="0.3">
       <c r="AL66" s="15"/>
       <c r="AM66" s="16"/>
       <c r="AN66" s="15"/>
@@ -10933,97 +10933,97 @@
       <c r="AV66" s="23"/>
       <c r="AW66" s="23"/>
     </row>
-    <row r="67" spans="38:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="38:49" ht="15.6" x14ac:dyDescent="0.3">
       <c r="AL67" s="15"/>
       <c r="AM67" s="16"/>
       <c r="AN67" s="15"/>
       <c r="AO67" s="17"/>
     </row>
-    <row r="68" spans="38:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="38:49" ht="15.6" x14ac:dyDescent="0.3">
       <c r="AL68" s="15"/>
       <c r="AM68" s="16"/>
       <c r="AN68" s="15"/>
       <c r="AO68" s="17"/>
     </row>
-    <row r="69" spans="38:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="38:49" ht="15.6" x14ac:dyDescent="0.3">
       <c r="AL69" s="15"/>
       <c r="AM69" s="16"/>
       <c r="AN69" s="15"/>
       <c r="AO69" s="17"/>
     </row>
-    <row r="70" spans="38:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="38:49" ht="15.6" x14ac:dyDescent="0.3">
       <c r="AL70" s="15"/>
       <c r="AM70" s="16"/>
       <c r="AN70" s="15"/>
       <c r="AO70" s="17"/>
     </row>
-    <row r="71" spans="38:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="38:49" ht="15.6" x14ac:dyDescent="0.3">
       <c r="AL71" s="15"/>
       <c r="AM71" s="16"/>
       <c r="AN71" s="15"/>
       <c r="AO71" s="17"/>
     </row>
-    <row r="72" spans="38:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="38:49" ht="15.6" x14ac:dyDescent="0.3">
       <c r="AL72" s="15"/>
       <c r="AM72" s="16"/>
       <c r="AN72" s="15"/>
       <c r="AO72" s="17"/>
     </row>
-    <row r="73" spans="38:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="38:49" ht="15.6" x14ac:dyDescent="0.3">
       <c r="AL73" s="15"/>
       <c r="AM73" s="16"/>
       <c r="AN73" s="15"/>
       <c r="AO73" s="17"/>
     </row>
-    <row r="74" spans="38:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="38:49" ht="15.6" x14ac:dyDescent="0.3">
       <c r="AL74" s="15"/>
       <c r="AM74" s="16"/>
       <c r="AN74" s="15"/>
       <c r="AO74" s="17"/>
     </row>
-    <row r="75" spans="38:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="38:49" ht="15.6" x14ac:dyDescent="0.3">
       <c r="AL75" s="15"/>
       <c r="AM75" s="16"/>
       <c r="AN75" s="15"/>
       <c r="AO75" s="17"/>
     </row>
-    <row r="76" spans="38:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="38:49" ht="15.6" x14ac:dyDescent="0.3">
       <c r="AL76" s="15"/>
       <c r="AM76" s="16"/>
       <c r="AN76" s="15"/>
       <c r="AO76" s="17"/>
     </row>
-    <row r="77" spans="38:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="38:49" ht="15.6" x14ac:dyDescent="0.3">
       <c r="AL77" s="15"/>
       <c r="AM77" s="16"/>
       <c r="AN77" s="15"/>
       <c r="AO77" s="17"/>
     </row>
-    <row r="78" spans="38:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="38:49" ht="15.6" x14ac:dyDescent="0.3">
       <c r="AL78" s="15"/>
       <c r="AM78" s="16"/>
       <c r="AN78" s="15"/>
       <c r="AO78" s="17"/>
     </row>
-    <row r="79" spans="38:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="38:49" ht="15.6" x14ac:dyDescent="0.3">
       <c r="AL79" s="15"/>
       <c r="AM79" s="16"/>
       <c r="AN79" s="15"/>
       <c r="AO79" s="17"/>
     </row>
-    <row r="80" spans="38:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="38:49" ht="15.6" x14ac:dyDescent="0.3">
       <c r="AL80" s="15"/>
       <c r="AM80" s="16"/>
       <c r="AN80" s="15"/>
       <c r="AO80" s="17"/>
     </row>
-    <row r="81" spans="38:41" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="38:41" ht="15.6" x14ac:dyDescent="0.3">
       <c r="AL81" s="15"/>
       <c r="AM81" s="16"/>
       <c r="AN81" s="15"/>
       <c r="AO81" s="17"/>
     </row>
-    <row r="82" spans="38:41" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="38:41" ht="15.6" x14ac:dyDescent="0.3">
       <c r="AL82" s="15"/>
       <c r="AM82" s="16"/>
       <c r="AN82" s="15"/>
